--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4460,27 +4460,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>108679001</v>
+        <v>137138372</v>
       </c>
       <c r="B35" t="n">
-        <v>58636</v>
+        <v>57849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>102621</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4490,30 +4490,34 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Stenramen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558109</v>
+        <v>558423</v>
       </c>
       <c r="R35" t="n">
-        <v>6628274</v>
+        <v>6627837</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4537,22 +4541,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4567,27 +4571,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108679001</t>
+          <t>https://artportalen.se/Sighting/137138372</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109873645</v>
+        <v>108679001</v>
       </c>
       <c r="B36" t="n">
-        <v>8455</v>
+        <v>58636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4595,46 +4599,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558205</v>
+        <v>558109</v>
       </c>
       <c r="R36" t="n">
-        <v>6628601</v>
+        <v>6628274</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4658,22 +4665,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,19 +4689,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Barrblandskog, lövinslag</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4710,13 +4706,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109873645</t>
+          <t>https://artportalen.se/Sighting/108679001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112203601</v>
+        <v>109873645</v>
       </c>
       <c r="B37" t="n">
         <v>8455</v>
@@ -4756,14 +4752,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558087</v>
+        <v>558205</v>
       </c>
       <c r="R37" t="n">
-        <v>6627982</v>
+        <v>6628601</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4790,12 +4786,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4810,7 +4816,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -4832,13 +4838,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112203601</t>
+          <t>https://artportalen.se/Sighting/109873645</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112501295</v>
+        <v>112203601</v>
       </c>
       <c r="B38" t="n">
         <v>8455</v>
@@ -4878,17 +4884,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558049</v>
+        <v>558087</v>
       </c>
       <c r="R38" t="n">
-        <v>6628477</v>
+        <v>6627982</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4912,12 +4918,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4932,7 +4938,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Tallskog, inslag av unga granplantor</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -4954,63 +4960,60 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501295</t>
+          <t>https://artportalen.se/Sighting/112203601</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>98358713</v>
+        <v>112501295</v>
       </c>
       <c r="B39" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stenramen, Ramnäs sn, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558097</v>
+        <v>558049</v>
       </c>
       <c r="R39" t="n">
-        <v>6627869</v>
+        <v>6628477</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5037,27 +5040,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5066,88 +5054,91 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Tallskog, inslag av unga granplantor</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Däggdjursinventering Surahammar</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98358713</t>
+          <t>https://artportalen.se/Sighting/112501295</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112457599</v>
+        <v>98358713</v>
       </c>
       <c r="B40" t="n">
-        <v>99118</v>
+        <v>56522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Stenramen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558038</v>
+        <v>558097</v>
       </c>
       <c r="R40" t="n">
-        <v>6628211</v>
+        <v>6627869</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5174,12 +5165,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5188,36 +5194,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Mossig gammal barrblandskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Däggdjursinventering Surahammar</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112457599</t>
+          <t>https://artportalen.se/Sighting/98358713</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112501403</v>
+        <v>112457599</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5247,7 +5251,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5264,14 +5268,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557958</v>
+        <v>558038</v>
       </c>
       <c r="R41" t="n">
-        <v>6628535</v>
+        <v>6628211</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5298,12 +5302,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5318,7 +5322,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Mossig gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5335,13 +5339,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501403</t>
+          <t>https://artportalen.se/Sighting/112457599</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112501658</v>
+        <v>112501403</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5371,7 +5375,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5392,10 +5396,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557921</v>
+        <v>557958</v>
       </c>
       <c r="R42" t="n">
-        <v>6628494</v>
+        <v>6628535</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5459,43 +5463,43 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501658</t>
+          <t>https://artportalen.se/Sighting/112501403</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>73394045</v>
+        <v>112501658</v>
       </c>
       <c r="B43" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5503,19 +5507,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558373</v>
+        <v>557921</v>
       </c>
       <c r="R43" t="n">
-        <v>6628146</v>
+        <v>6628494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5542,12 +5550,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5562,7 +5570,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5579,16 +5587,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73394045</t>
+          <t>https://artportalen.se/Sighting/112501658</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>73391459</v>
+        <v>73394045</v>
       </c>
       <c r="B44" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5596,26 +5604,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5628,14 +5636,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558245</v>
+        <v>558373</v>
       </c>
       <c r="R44" t="n">
-        <v>6628005</v>
+        <v>6628146</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5699,13 +5707,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73391459</t>
+          <t>https://artportalen.se/Sighting/73394045</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112164100</v>
+        <v>73391459</v>
       </c>
       <c r="B45" t="n">
         <v>97989</v>
@@ -5733,21 +5741,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558020</v>
+        <v>558245</v>
       </c>
       <c r="R45" t="n">
-        <v>6628293</v>
+        <v>6628005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5774,12 +5790,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5794,7 +5810,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5811,16 +5827,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112164100</t>
+          <t>https://artportalen.se/Sighting/73391459</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112204071</v>
+        <v>112164100</v>
       </c>
       <c r="B46" t="n">
-        <v>97977</v>
+        <v>97989</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5828,45 +5844,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221944</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558130</v>
+        <v>558020</v>
       </c>
       <c r="R46" t="n">
-        <v>6628068</v>
+        <v>6628293</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5890,12 +5902,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5910,12 +5922,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>på mossigt block</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5932,16 +5939,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112204071</t>
+          <t>https://artportalen.se/Sighting/112164100</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>73391737</v>
+        <v>112204071</v>
       </c>
       <c r="B47" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5949,41 +5956,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558527</v>
+        <v>558130</v>
       </c>
       <c r="R47" t="n">
-        <v>6628111</v>
+        <v>6628068</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6007,12 +6018,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6027,7 +6038,12 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>på mossigt block</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6044,16 +6060,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73391737</t>
+          <t>https://artportalen.se/Sighting/112204071</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>100803900</v>
+        <v>73391737</v>
       </c>
       <c r="B48" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,16 +6077,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6085,14 +6101,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558564</v>
+        <v>558527</v>
       </c>
       <c r="R48" t="n">
-        <v>6628255</v>
+        <v>6628111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6119,12 +6135,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6150,19 +6166,19 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lise-Lotte Norin</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100803900</t>
+          <t>https://artportalen.se/Sighting/73391737</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>109873621</v>
+        <v>100803900</v>
       </c>
       <c r="B49" t="n">
         <v>97986</v>
@@ -6197,17 +6213,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558205</v>
+        <v>558564</v>
       </c>
       <c r="R49" t="n">
-        <v>6628601</v>
+        <v>6628255</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6231,22 +6247,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6261,7 +6267,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6272,19 +6278,19 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Lise-Lotte Norin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109873621</t>
+          <t>https://artportalen.se/Sighting/100803900</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124519006</v>
+        <v>109873621</v>
       </c>
       <c r="B50" t="n">
         <v>97986</v>
@@ -6319,17 +6325,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kölberget, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558532</v>
+        <v>558205</v>
       </c>
       <c r="R50" t="n">
-        <v>6628372</v>
+        <v>6628601</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6353,12 +6359,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6373,7 +6389,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6389,6 +6405,118 @@
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109873621</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124519006</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kölberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>558532</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6628372</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124519006</t>
         </is>
@@ -6445,6 +6573,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4463,7 +4463,7 @@
         <v>137138372</v>
       </c>
       <c r="B35" t="n">
-        <v>57849</v>
+        <v>57862</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4463,7 +4463,7 @@
         <v>137138372</v>
       </c>
       <c r="B35" t="n">
-        <v>57862</v>
+        <v>57864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4494,16 +4494,8 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4463,7 +4463,7 @@
         <v>137138372</v>
       </c>
       <c r="B35" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4463,7 +4463,7 @@
         <v>137138372</v>
       </c>
       <c r="B35" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4327,32 +4327,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126260723</v>
+        <v>137397597</v>
       </c>
       <c r="B34" t="n">
-        <v>57141</v>
+        <v>93507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4360,31 +4360,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Månses hål , Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558085</v>
+        <v>558109</v>
       </c>
       <c r="R34" t="n">
-        <v>6628591</v>
+        <v>6628490</v>
       </c>
       <c r="S34" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4408,27 +4403,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Flög in mot Ulvsbomurens NR</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4437,55 +4417,61 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Tallskog, ris- och renlavsmarker</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126260723</t>
+          <t>https://artportalen.se/Sighting/137397597</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137138372</v>
+        <v>126260723</v>
       </c>
       <c r="B35" t="n">
-        <v>57875</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4494,22 +4480,30 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stenramen, Ramnäs sn, Vstm</t>
+          <t>Månses hål , Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558423</v>
+        <v>558085</v>
       </c>
       <c r="R35" t="n">
-        <v>6627837</v>
+        <v>6628591</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4533,22 +4527,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Flög in mot Ulvsbomurens NR</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4563,44 +4562,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137138372</t>
+          <t>https://artportalen.se/Sighting/126260723</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>108679001</v>
+        <v>137138372</v>
       </c>
       <c r="B36" t="n">
-        <v>58636</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>102621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4610,30 +4609,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Stenramen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558109</v>
+        <v>558423</v>
       </c>
       <c r="R36" t="n">
-        <v>6628274</v>
+        <v>6627837</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4657,22 +4652,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4687,27 +4682,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108679001</t>
+          <t>https://artportalen.se/Sighting/137138372</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109873645</v>
+        <v>108679001</v>
       </c>
       <c r="B37" t="n">
-        <v>8455</v>
+        <v>58636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,46 +4710,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558205</v>
+        <v>558109</v>
       </c>
       <c r="R37" t="n">
-        <v>6628601</v>
+        <v>6628274</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4778,22 +4776,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4802,19 +4800,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog, lövinslag</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4830,13 +4817,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109873645</t>
+          <t>https://artportalen.se/Sighting/108679001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112203601</v>
+        <v>109873645</v>
       </c>
       <c r="B38" t="n">
         <v>8455</v>
@@ -4876,14 +4863,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558087</v>
+        <v>558205</v>
       </c>
       <c r="R38" t="n">
-        <v>6627982</v>
+        <v>6628601</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4910,12 +4897,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4930,7 +4927,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -4952,13 +4949,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112203601</t>
+          <t>https://artportalen.se/Sighting/109873645</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112501295</v>
+        <v>112203601</v>
       </c>
       <c r="B39" t="n">
         <v>8455</v>
@@ -4998,17 +4995,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558049</v>
+        <v>558087</v>
       </c>
       <c r="R39" t="n">
-        <v>6628477</v>
+        <v>6627982</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5032,12 +5029,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,7 +5049,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Tallskog, inslag av unga granplantor</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5074,63 +5071,60 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501295</t>
+          <t>https://artportalen.se/Sighting/112203601</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98358713</v>
+        <v>112501295</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stenramen, Ramnäs sn, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558097</v>
+        <v>558049</v>
       </c>
       <c r="R40" t="n">
-        <v>6627869</v>
+        <v>6628477</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5157,27 +5151,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5186,88 +5165,91 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Tallskog, inslag av unga granplantor</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Däggdjursinventering Surahammar</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98358713</t>
+          <t>https://artportalen.se/Sighting/112501295</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112457599</v>
+        <v>98358713</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>56522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Stenramen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558038</v>
+        <v>558097</v>
       </c>
       <c r="R41" t="n">
-        <v>6628211</v>
+        <v>6627869</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5294,12 +5276,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5308,36 +5305,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Mossig gammal barrblandskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Däggdjursinventering Surahammar</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112457599</t>
+          <t>https://artportalen.se/Sighting/98358713</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112501403</v>
+        <v>112457599</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5384,14 +5379,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557958</v>
+        <v>558038</v>
       </c>
       <c r="R42" t="n">
-        <v>6628535</v>
+        <v>6628211</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5418,12 +5413,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5438,7 +5433,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Mossig gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5455,13 +5450,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501403</t>
+          <t>https://artportalen.se/Sighting/112457599</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112501658</v>
+        <v>112501403</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5491,7 +5486,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557921</v>
+        <v>557958</v>
       </c>
       <c r="R43" t="n">
-        <v>6628494</v>
+        <v>6628535</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5579,43 +5574,43 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112501658</t>
+          <t>https://artportalen.se/Sighting/112501403</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>73394045</v>
+        <v>112501658</v>
       </c>
       <c r="B44" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5623,19 +5618,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558373</v>
+        <v>557921</v>
       </c>
       <c r="R44" t="n">
-        <v>6628146</v>
+        <v>6628494</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5662,12 +5661,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5682,7 +5681,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5699,16 +5698,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73394045</t>
+          <t>https://artportalen.se/Sighting/112501658</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>73391459</v>
+        <v>73394045</v>
       </c>
       <c r="B45" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5716,26 +5715,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5748,14 +5747,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558245</v>
+        <v>558373</v>
       </c>
       <c r="R45" t="n">
-        <v>6628005</v>
+        <v>6628146</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5819,13 +5818,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73391459</t>
+          <t>https://artportalen.se/Sighting/73394045</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112164100</v>
+        <v>73391459</v>
       </c>
       <c r="B46" t="n">
         <v>97989</v>
@@ -5853,21 +5852,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558020</v>
+        <v>558245</v>
       </c>
       <c r="R46" t="n">
-        <v>6628293</v>
+        <v>6628005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5894,12 +5901,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5914,7 +5921,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5931,16 +5938,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112164100</t>
+          <t>https://artportalen.se/Sighting/73391459</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112204071</v>
+        <v>112164100</v>
       </c>
       <c r="B47" t="n">
-        <v>97977</v>
+        <v>97989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5948,45 +5955,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221944</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558130</v>
+        <v>558020</v>
       </c>
       <c r="R47" t="n">
-        <v>6628068</v>
+        <v>6628293</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6010,12 +6013,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6030,12 +6033,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>på mossigt block</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6052,16 +6050,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112204071</t>
+          <t>https://artportalen.se/Sighting/112164100</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73391737</v>
+        <v>112204071</v>
       </c>
       <c r="B48" t="n">
-        <v>97983</v>
+        <v>97977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6069,41 +6067,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558527</v>
+        <v>558130</v>
       </c>
       <c r="R48" t="n">
-        <v>6628111</v>
+        <v>6628068</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6127,12 +6129,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6147,7 +6149,12 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>på mossigt block</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6164,16 +6171,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73391737</t>
+          <t>https://artportalen.se/Sighting/112204071</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>100803900</v>
+        <v>73391737</v>
       </c>
       <c r="B49" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6181,16 +6188,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6205,14 +6212,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558564</v>
+        <v>558527</v>
       </c>
       <c r="R49" t="n">
-        <v>6628255</v>
+        <v>6628111</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,12 +6246,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6270,19 +6277,19 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lise-Lotte Norin</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100803900</t>
+          <t>https://artportalen.se/Sighting/73391737</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>109873621</v>
+        <v>100803900</v>
       </c>
       <c r="B50" t="n">
         <v>97986</v>
@@ -6317,17 +6324,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558205</v>
+        <v>558564</v>
       </c>
       <c r="R50" t="n">
-        <v>6628601</v>
+        <v>6628255</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6351,22 +6358,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2022-05-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6381,7 +6378,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6392,19 +6389,19 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Tom Sävström, Lise-Lotte Norin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109873621</t>
+          <t>https://artportalen.se/Sighting/100803900</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124519006</v>
+        <v>109873621</v>
       </c>
       <c r="B51" t="n">
         <v>97986</v>
@@ -6439,17 +6436,17 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kölberget, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558532</v>
+        <v>558205</v>
       </c>
       <c r="R51" t="n">
-        <v>6628372</v>
+        <v>6628601</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6473,12 +6470,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6493,7 +6500,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, lövinslag</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6509,6 +6516,118 @@
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109873621</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124519006</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kölberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>558532</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6628372</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124519006</t>
         </is>
@@ -6566,6 +6685,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4330,7 +4330,7 @@
         <v>137397597</v>
       </c>
       <c r="B34" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4330,7 +4330,7 @@
         <v>137397597</v>
       </c>
       <c r="B34" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4330,7 +4330,7 @@
         <v>137397597</v>
       </c>
       <c r="B34" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -4330,7 +4330,7 @@
         <v>137397597</v>
       </c>
       <c r="B34" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>137138372</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
